--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-02-2026.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£9.77</t>
+          <t>£10.74</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£10.48</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>£10.24</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£11.89</t>
+          <t>£13.07</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£12.15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>£14.44</t>
+          <t>£15.87</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£14.77</t>
+          <t>£14.89</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>£15.4</t>
+          <t>£16.96</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£16.00</t>
+          <t>£15.99</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>£19.19</t>
+          <t>£21.12</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£19.75</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>£21.62</t>
+          <t>£23.8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£22.06</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>£20.97</t>
+          <t>£23.05</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£22.13</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>£23.83</t>
+          <t>£26.23</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£25.47</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>£31.88</t>
+          <t>£35.09</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>£32.14</t>
+          <t>£32.42</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>£32.98</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£33.38</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£33.04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>£41.12</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.99</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>£44.39</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£42.35</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£39.69</t>
+          <t>£40.05</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>£39.6</t>
+          <t>£43.55</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>£634.53</t>
+          <t>£697.98</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£779.88</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>£853.62</t>
+          <t>£939.1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1019.88</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>£40.65</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£28.55</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>£48.65</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>£57.54</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>£55.49</t>
+          <t>£61.03</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£42.55</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>£41.25</t>
+          <t>£45.36</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£48.17</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>£43.3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.58</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1,016.40</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>£44.58</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.08</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>£1057.71</t>
+          <t>£1163.76</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1267.2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>£1126.15</t>
+          <t>£1238.58</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>£1096.66</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-140mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
